--- a/nord-kivu/sortie/zs/Katwa/Tableaux_ZS_Katwa_20261014.xlsx
+++ b/nord-kivu/sortie/zs/Katwa/Tableaux_ZS_Katwa_20261014.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bulletin des aires'!$A$1:$P$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bulletin des aires'!$A$1:$P$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cas'!$A$1:$S$667</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,11 +452,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -558,25 +558,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Iranga</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -585,25 +582,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Irangya</t>
+          <t>Bughenda</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>27</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -612,25 +606,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ivatama</t>
+          <t>Butembo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>67</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -639,25 +630,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kambuli</t>
+          <t>Byasa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>29</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -666,25 +654,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kangothe</t>
+          <t>C.H Mukuna</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>32</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -693,25 +678,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kavisa</t>
+          <t>Cemebu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>129</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -720,27 +702,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kihinga</t>
+          <t>Ch Saint Peregrin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>11</v>
-      </c>
-      <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
@@ -750,25 +726,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kimbulu</t>
+          <t>Chimutiri</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>83</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -777,25 +750,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kiriva</t>
+          <t>Cs Muchanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>44</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -804,27 +774,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kivika</t>
+          <t>Hgr</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
@@ -834,27 +798,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kyaghala</t>
+          <t>Hgr Katwa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
@@ -864,25 +822,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kyambogho</t>
+          <t>Hgr Matanda</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>73</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -891,7 +846,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kyangike</t>
+          <t>Iranga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -909,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -918,28 +873,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Makangala</t>
+          <t>Irangya</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Jaune</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>9</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -948,12 +900,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Makarere</t>
+          <t>Ivatama</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Verte</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -963,13 +915,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -978,27 +927,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Makerere</t>
+          <t>Kakivika</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
@@ -1008,25 +951,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Masereka</t>
+          <t>Kakohwa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>72</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1035,27 +975,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Masiki</t>
+          <t>Kakuva</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
@@ -1065,27 +999,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Masuli</t>
+          <t>Kalemire</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
@@ -1095,27 +1023,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Matanda</t>
+          <t>Kaleveryo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>11</v>
-      </c>
-      <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
@@ -1125,25 +1047,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mihake</t>
+          <t>Kalunguta</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>82</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1152,7 +1071,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Misebere</t>
+          <t>Kambuli</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1161,7 +1080,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1179,27 +1098,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mitoya</t>
+          <t>Kampulu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6</v>
-      </c>
-      <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
@@ -1209,16 +1122,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mondo</t>
+          <t>Kangothe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Jaune</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1227,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1236,27 +1149,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Muchanga</t>
+          <t>Karasaba</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6</v>
-      </c>
-      <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
@@ -1266,27 +1173,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mukuna</t>
+          <t>Katwa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
@@ -1296,12 +1197,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Muthiri</t>
+          <t>Kavisa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Verte</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1314,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1323,25 +1224,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mutiri</t>
+          <t>Kayilavula</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>30</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1350,27 +1248,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mutsanga</t>
+          <t>Kiaghala</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>9</v>
-      </c>
-      <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
@@ -1380,25 +1272,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Kihinga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1410,16 +1302,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Rughenda</t>
+          <t>Kimbulu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Verte</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1428,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -1437,16 +1329,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tulizeni</t>
+          <t>Kiriva</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Verte</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1455,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -1464,25 +1356,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Utulivu</t>
+          <t>Kisanga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>74</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -1491,27 +1380,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Vighole</t>
+          <t>Kisingali</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
-      </c>
-      <c r="G35" t="n">
-        <v>9</v>
-      </c>
-      <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
@@ -1521,27 +1404,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Vuhika</t>
+          <t>Kivaka</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
-        <v>12</v>
-      </c>
-      <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
@@ -1551,7 +1428,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Vungi</t>
+          <t>Kivika</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1560,16 +1437,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1581,25 +1458,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Vutahira</t>
+          <t>Kyaghala</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G38" t="n">
-        <v>22</v>
+        <v>6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -1608,27 +1488,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Vutetse</t>
+          <t>Kyahala</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>7</v>
-      </c>
-      <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
@@ -1638,25 +1512,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Vuthahira</t>
+          <t>Kyalihali</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>63</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -1665,7 +1536,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Vutsundo</t>
+          <t>Kyambogho</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1674,7 +1545,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1683,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -1692,12 +1563,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Vuvatsi</t>
+          <t>Kyangike</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Jaune</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1710,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -1719,27 +1590,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Wanamahika</t>
+          <t>Lakerere</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
-      </c>
-      <c r="G43" t="n">
-        <v>5</v>
-      </c>
-      <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
@@ -1749,35 +1614,1682 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Makangala</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>15</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Makangaza</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Makarere</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>12</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Makasi</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Makengela</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Makerere</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>9</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Makuna</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Malera</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Mangi</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Masereka</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Verte</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>72</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Maserere</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Masiki</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>18</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Masudo</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Masule</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Masuli</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>101</v>
+      </c>
+      <c r="D58" t="n">
+        <v>6</v>
+      </c>
+      <c r="E58" t="n">
+        <v>12</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Matanda</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>11</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Mihake</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Verte</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>82</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Misebere</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Jaune</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>29</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Mitoya</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>6</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Mizebere</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Mondo</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Verte</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>83</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Msauli</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Muchanga</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>6</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Mukangala</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Mukuna</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>19</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Musayi</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Musebere</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Musimba</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Musuli</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Muthiri</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Jaune</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>40</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Mutiri</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Jaune</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Mutsanga</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>9</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Muyisa</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ngeleza</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ngingi</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ngothe</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ruenda</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Rughenda</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Jaune</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>23</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>25</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Ruwenda</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Rwenda</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Tulizani</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Tulizeni</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Jaune</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>7</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>33</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Tuulizeni</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Utulivu</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Verte</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>74</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Vighole</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>10</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" t="n">
+        <v>9</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Visoho</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Vuamahika</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Vughole</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Vuhika</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>5</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>12</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Vuhunga</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Vukaka</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Vungi</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>202</v>
+      </c>
+      <c r="D96" t="n">
+        <v>16</v>
+      </c>
+      <c r="E96" t="n">
+        <v>44</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Vungu</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Vusenzera</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Vutahira</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Jaune</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>22</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Vutetse</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>5</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
+        <v>7</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Vuthahira</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Verte</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>63</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Vutike</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Vutsundo</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Verte</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>58</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Vuvatsi</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>21</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Wanamaha</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Wanamahika</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>56</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>6</v>
+      </c>
+      <c r="G106" t="n">
+        <v>5</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>Wayene</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Rouge</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C107" t="n">
         <v>18</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D107" t="n">
         <v>2</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E107" t="n">
         <v>4</v>
       </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P44"/>
+  <autoFilter ref="A1:P107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
